--- a/test/fixtures/files/participantes.xlsx
+++ b/test/fixtures/files/participantes.xlsx
@@ -1,274 +1,601 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <workbookPr date1904="false"/>
   <sheets>
-    <sheet name="Participantes" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Hoja1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="2">
+    <numFmt formatCode="yyyy/mm/dd" numFmtId="100"/>
+    <numFmt formatCode="yyyy/mm/dd hh:mm:ss" numFmtId="101"/>
+  </numFmts>
   <fonts count="1">
     <font>
+      <name val="Arial"/>
       <sz val="11"/>
-      <name val="Calibri"/>
+      <family val="1"/>
     </font>
   </fonts>
-  <fills count="1">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border/>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf xfId="0"/>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0"/>
+  </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16" count="0"/>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="1F497D"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="EEECE1"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4F81BD"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="C0504D"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9BBB59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064A2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4BACC6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="F79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="800080"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="false"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="false">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="false">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="false">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
+  <a:extraClrSchemeLst/>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
+  <cols>
+    <col width="9.9" min="1" max="1" bestFit="1" customWidth="1"/>
+    <col width="12.100000000000001" min="2" max="2" bestFit="1" customWidth="1"/>
+    <col width="7.700000000000001" min="3" max="3" bestFit="1" customWidth="1"/>
+    <col width="9.9" min="4" max="4" bestFit="1" customWidth="1"/>
+    <col width="19.8" min="5" max="5" bestFit="1" customWidth="1"/>
+    <col width="19.8" min="6" max="6" bestFit="1" customWidth="1"/>
+    <col width="9.9" min="7" max="7" bestFit="1" customWidth="1"/>
+    <col width="9.9" min="8" max="8" bestFit="1" customWidth="1"/>
+    <col width="12.100000000000001" min="9" max="9" bestFit="1" customWidth="1"/>
+    <col width="13.200000000000001" min="10" max="10" bestFit="1" customWidth="1"/>
+    <col width="12.100000000000001" min="11" max="11" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="0" t="inlineStr">
         <is>
           <t>Nombre</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="0" t="inlineStr">
         <is>
           <t>Apellido</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="0" t="inlineStr">
         <is>
           <t>Edad</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="0" t="inlineStr">
         <is>
           <t>Género</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="0" t="inlineStr">
         <is>
           <t>Estaca</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="0" t="inlineStr">
         <is>
           <t>Barrio</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="0" t="inlineStr">
         <is>
           <t>Camisa</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="0" t="inlineStr">
         <is>
           <t>Cuarto</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="0" t="inlineStr">
         <is>
           <t>Compañía</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="0" t="inlineStr">
         <is>
           <t>Teléfono</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="0" t="inlineStr">
         <is>
           <t>Alergias</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="0" t="inlineStr">
         <is>
           <t>Ana</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="0" t="inlineStr">
         <is>
           <t>Ruiz</t>
         </is>
       </c>
-      <c r="C2">
+      <c r="C2" s="0" t="n">
         <v>15</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="0" t="inlineStr">
         <is>
           <t>Mujer</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="0" t="inlineStr">
         <is>
           <t>Las Americas</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="0" t="inlineStr">
         <is>
           <t>Ciudad Jardin</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="0" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="I2">
+      <c r="H2" s="0" t="n">
+        <v>101</v>
+      </c>
+      <c r="I2" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" s="0" t="inlineStr">
         <is>
           <t>8888-1111</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K2" s="0" t="inlineStr">
         <is>
           <t>Maní</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="0" t="inlineStr">
         <is>
           <t>Carlos</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="0" t="inlineStr">
         <is>
           <t>Mena</t>
         </is>
       </c>
-      <c r="C3">
+      <c r="C3" s="0" t="n">
         <v>16</v>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="0" t="inlineStr">
         <is>
           <t>Hombre</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="0" t="inlineStr">
         <is>
           <t>Bello Horizonte</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Ducuali</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="F3" s="0" t="inlineStr">
+        <is>
+          <t>La Rotonda</t>
+        </is>
+      </c>
+      <c r="G3" s="0" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
-      <c r="I3">
+      <c r="H3" s="0" t="n">
+        <v>202</v>
+      </c>
+      <c r="I3" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="0" t="inlineStr">
         <is>
           <t>8888-2222</t>
         </is>
       </c>
+      <c r="K3" s="0"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="0" t="inlineStr">
         <is>
           <t>Sofía</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="0" t="inlineStr">
         <is>
           <t>Lopez</t>
         </is>
       </c>
-      <c r="C4">
+      <c r="C4" s="0" t="n">
         <v>17</v>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="0" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="0" t="inlineStr">
         <is>
           <t>Villa Flor</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>La Rotonda</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="F4" s="0" t="inlineStr">
+        <is>
+          <t>Primavera</t>
+        </is>
+      </c>
+      <c r="G4" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="I4">
+      <c r="H4" s="0" t="n">
+        <v>103</v>
+      </c>
+      <c r="I4" s="0" t="n">
         <v>99</v>
       </c>
+      <c r="J4" s="0"/>
+      <c r="K4" s="0"/>
     </row>
-    <row r="5"/>
+    <row r="5">
+      <c r="A5" s="0"/>
+      <c r="B5" s="0"/>
+      <c r="C5" s="0"/>
+      <c r="D5" s="0"/>
+      <c r="E5" s="0"/>
+      <c r="F5" s="0"/>
+      <c r="G5" s="0"/>
+      <c r="H5" s="0"/>
+      <c r="I5" s="0"/>
+      <c r="J5" s="0"/>
+      <c r="K5" s="0"/>
+    </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="0" t="inlineStr">
         <is>
           <t>Pedro</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="0" t="inlineStr">
         <is>
           <t>SinEdad</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="C6" s="0"/>
+      <c r="D6" s="0" t="inlineStr">
         <is>
           <t>Hombre</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="0" t="inlineStr">
         <is>
           <t>Las Americas</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Waspan</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="F6" s="0" t="inlineStr">
+        <is>
+          <t>La Maximo Jerez</t>
+        </is>
+      </c>
+      <c r="G6" s="0" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
+      <c r="H6" s="0"/>
+      <c r="I6" s="0"/>
+      <c r="J6" s="0"/>
+      <c r="K6" s="0"/>
     </row>
   </sheetData>
+  <sheetCalcPr fullCalcOnLoad="1"/>
+  <printOptions gridLines="0" headings="0" horizontalCentered="0" verticalCentered="0"/>
+  <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
+  <pageSetup/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/test/fixtures/files/participantes.xlsx
+++ b/test/fixtures/files/participantes.xlsx
@@ -335,7 +335,7 @@
     <col width="7.700000000000001" min="3" max="3" bestFit="1" customWidth="1"/>
     <col width="9.9" min="4" max="4" bestFit="1" customWidth="1"/>
     <col width="19.8" min="5" max="5" bestFit="1" customWidth="1"/>
-    <col width="19.8" min="6" max="6" bestFit="1" customWidth="1"/>
+    <col width="24.200000000000003" min="6" max="6" bestFit="1" customWidth="1"/>
     <col width="9.9" min="7" max="7" bestFit="1" customWidth="1"/>
     <col width="9.9" min="8" max="8" bestFit="1" customWidth="1"/>
     <col width="12.100000000000001" min="9" max="9" bestFit="1" customWidth="1"/>
@@ -426,7 +426,7 @@
       </c>
       <c r="F2" s="0" t="inlineStr">
         <is>
-          <t>Ciudad Jardin</t>
+          <t>Barrio Las Mercedes</t>
         </is>
       </c>
       <c r="G2" s="0" t="inlineStr">
@@ -524,7 +524,7 @@
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
-          <t>Primavera</t>
+          <t>Los Laureles</t>
         </is>
       </c>
       <c r="G4" s="0" t="inlineStr">
@@ -578,7 +578,7 @@
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
-          <t>La Maximo Jerez</t>
+          <t>Ciudadela</t>
         </is>
       </c>
       <c r="G6" s="0" t="inlineStr">
